--- a/docs/oc-regiones/alimentos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/alimentos/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M640"/>
+  <dimension ref="A1:M646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3408.63</v>
+        <v>3379.76</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>11424.01</v>
+        <v>11327.26</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8747.75</v>
+        <v>8673.66</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>749.22</v>
+        <v>745.37</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13265.69</v>
+        <v>13133.29</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2521.88</v>
+        <v>2496.71</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1311.67</v>
+        <v>1298.58</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>743.96</v>
+        <v>736.54</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3013.79</v>
+        <v>2982.23</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>755.16</v>
+        <v>747.25</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2271.99</v>
+        <v>2259.58</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>59079.03</v>
+        <v>58420.8</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2179.36</v>
+        <v>2155.08</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2400.46</v>
+        <v>2373.71</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1579.66</v>
+        <v>1562.06</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3588.55</v>
+        <v>3548.57</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>763.96</v>
+        <v>759.78</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>743.33</v>
+        <v>742.38</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2398.75</v>
+        <v>2395.69</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>755.29</v>
+        <v>757.77</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1598.65</v>
+        <v>1603.91</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1783.78</v>
+        <v>1789.65</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>5243.22</v>
+        <v>5333.73</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3428.99</v>
+        <v>3488.18</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>40878</v>
+        <v>40709.52</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1245.57</v>
+        <v>1243.64</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>745.7</v>
+        <v>744.54</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1583.62</v>
+        <v>1581.17</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4938.73</v>
+        <v>4931.08</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2159.35</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>42187.13</v>
+        <v>42121.74</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3648.85</v>
+        <v>3667.69</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2681.54</v>
+        <v>2695.38</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>2908.63</v>
+        <v>2923.65</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6367.67</v>
+        <v>6400.55</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7714.17</v>
+        <v>7754.01</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2858.82</v>
+        <v>2873.59</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>10503.95</v>
+        <v>10558.2</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>25317.31</v>
+        <v>25448.06</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>4217.41</v>
+        <v>4239.19</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5389.99</v>
+        <v>5417.83</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>42136.77</v>
+        <v>42354.38</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>12797.3</v>
+        <v>12863.39</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>8927.4</v>
+        <v>8973.51</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1251.37</v>
+        <v>1260.2</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1351.89</v>
+        <v>1361.43</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>13595.93</v>
+        <v>13691.89</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>9942.32</v>
+        <v>10012.48</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6275.53</v>
+        <v>6319.82</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1174.42</v>
+        <v>1182.71</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>6168.66</v>
+        <v>6212.2</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5617.73</v>
+        <v>5657.38</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1245.49</v>
+        <v>1229.67</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>764.46</v>
+        <v>756.86</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>808.22</v>
+        <v>800.1799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>911.99</v>
+        <v>902.92</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2289.99</v>
+        <v>2267.2</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3538.98</v>
+        <v>3503.77</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12179.73</v>
+        <v>12058.55</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6499.9</v>
+        <v>6435.23</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3461.98</v>
+        <v>3427.54</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1302.85</v>
+        <v>1289.89</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1227.73</v>
+        <v>1215.51</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1737.16</v>
+        <v>1730.93</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1084.65</v>
+        <v>1080.76</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11929.09</v>
+        <v>11903.28</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>764.9299999999999</v>
+        <v>763.27</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3860.33</v>
+        <v>3851.98</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3087.76</v>
+        <v>3081.08</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1712.32</v>
+        <v>1708.61</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3917.49</v>
+        <v>3909.01</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2111.1</v>
+        <v>2106.53</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>839.55</v>
+        <v>837.73</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>11856.79</v>
+        <v>11807.08</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7074.71</v>
+        <v>7045.05</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5485.49</v>
+        <v>5462.49</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1279.08</v>
+        <v>1273.72</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>6378.89</v>
+        <v>6352.14</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3500.47</v>
+        <v>3485.79</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>49723.47</v>
+        <v>49515.01</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>4012.57</v>
+        <v>3995.74</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12852.19</v>
+        <v>12798.31</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>784.62</v>
+        <v>775.54</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>828.1900000000001</v>
+        <v>818.61</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1457.82</v>
+        <v>1440.95</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>1693.37</v>
+        <v>1673.77</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1459.06</v>
+        <v>1446.7</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4213.22</v>
+        <v>4177.53</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>36699.8</v>
+        <v>36670.3</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>17931.56</v>
+        <v>17917.14</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3482.46</v>
+        <v>3498.24</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>1002.01</v>
+        <v>1006.55</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1198.48</v>
+        <v>1201.65</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6367.84</v>
+        <v>6358.91</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>6427.23</v>
+        <v>6471.47</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1133.06</v>
+        <v>1142.74</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3816.9</v>
+        <v>3849.52</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3914.37</v>
+        <v>3962.48</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1517.86</v>
+        <v>1526.16</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1936.77</v>
+        <v>1947.36</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>44946.08</v>
+        <v>45191.88</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>15825.13</v>
+        <v>15911.67</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7647.65</v>
+        <v>7689.47</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>7661.41</v>
+        <v>7703.31</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>13247.92</v>
+        <v>13320.36</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>7187.83</v>
+        <v>7227.14</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4619.39</v>
+        <v>4644.65</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>24343.93</v>
+        <v>24477.06</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>41229.05</v>
+        <v>41454.52</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4443.59</v>
+        <v>4467.89</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3340.02</v>
+        <v>3358.28</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>14864.82</v>
+        <v>14485.24</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2495.87</v>
+        <v>2447.19</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2700.34</v>
+        <v>2661.64</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>3077.61</v>
+        <v>3033.5</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2271.57</v>
+        <v>2239.02</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>12406.92</v>
+        <v>12229.09</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>6474.07</v>
+        <v>6391.89</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1031.27</v>
+        <v>1018.18</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5443.62</v>
+        <v>5374.52</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>2089.87</v>
+        <v>2063.35</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2541.19</v>
+        <v>2508.94</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>1338.87</v>
+        <v>1321.88</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>4135.91</v>
+        <v>4083.41</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3076.15</v>
+        <v>3037.11</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3575</v>
+        <v>3529.62</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1565.2</v>
+        <v>1542.64</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>887.54</v>
+        <v>874.75</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>800.76</v>
+        <v>789.22</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3150.59</v>
+        <v>3109.87</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>3150.19</v>
+        <v>3143.99</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>20257.09</v>
+        <v>20257.22</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2067.95</v>
+        <v>2066.54</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2262.6</v>
+        <v>2261.05</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>6091.82</v>
+        <v>6070.91</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1201.42</v>
+        <v>1195.07</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>12928.52</v>
+        <v>12860.22</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>1747.26</v>
+        <v>1738.03</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3203.73</v>
+        <v>3186.8</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>14059.61</v>
+        <v>13985.35</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1714</v>
+        <v>1704.95</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>3845.13</v>
+        <v>3821.03</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>16638.75</v>
+        <v>16534.49</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>33739.08</v>
+        <v>33527.65</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>5327.34</v>
+        <v>5399.09</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2349.65</v>
+        <v>2381.29</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>792.52</v>
+        <v>803.1900000000001</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1574.72</v>
+        <v>1613.02</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>1191.34</v>
+        <v>1220.31</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1130.09</v>
+        <v>1157.57</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>2271.79</v>
+        <v>2327.03</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1246.43</v>
+        <v>1277.94</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2712.55</v>
+        <v>2781.12</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>6048.93</v>
+        <v>6201.85</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>52090.32</v>
+        <v>53407.17</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>37741.75</v>
+        <v>38695.86</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2689.24</v>
+        <v>2757.23</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>56859.5</v>
+        <v>58296.91</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>13451.46</v>
+        <v>13791.51</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>11673.55</v>
+        <v>11968.66</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2007.32</v>
+        <v>2068.19</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>5126.33</v>
+        <v>5281.78</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2744.56</v>
+        <v>2826.14</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3245.67</v>
+        <v>3342.14</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1278.01</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1652.25</v>
+        <v>1701.36</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>961.45</v>
+        <v>990.03</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3934.15</v>
+        <v>4051.09</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>1031.11</v>
+        <v>1061.76</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>6580.19</v>
+        <v>6775.77</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1027.75</v>
+        <v>1058.29</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1132.72</v>
+        <v>1166.39</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2900.02</v>
+        <v>2986.22</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1827.17</v>
+        <v>1881.48</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>5763.07</v>
+        <v>5934.37</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>4537.42</v>
+        <v>4672.28</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>7205.48</v>
+        <v>7419.65</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>5773.07</v>
+        <v>5944.67</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>7003.94</v>
+        <v>7212.11</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>10604.96</v>
+        <v>10920.17</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1032.92</v>
+        <v>1029.25</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1292.85</v>
+        <v>1288.25</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>921.9299999999999</v>
+        <v>918.65</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>10073.08</v>
+        <v>10037.22</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>13038.11</v>
+        <v>12991.69</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>6198.19</v>
+        <v>6151.8</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>25471.37</v>
+        <v>25280.74</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>6233.58</v>
+        <v>6186.93</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>3957.51</v>
+        <v>3927.89</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1485</v>
+        <v>1489.3</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2220.9</v>
+        <v>2227.33</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5486.18</v>
+        <v>5502.08</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>9739.91</v>
+        <v>9790.23</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>16005.39</v>
+        <v>16088.07</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3550.8</v>
+        <v>3569.14</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>3475.09</v>
+        <v>3493.04</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>5883</v>
+        <v>5913.39</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1203.43</v>
+        <v>1198.35</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1751.7</v>
+        <v>1744.32</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>814.88</v>
+        <v>811.4400000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2246.18</v>
+        <v>2236.71</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1038.64</v>
+        <v>1034.26</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>1081.82</v>
+        <v>1077.26</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>951.0599999999999</v>
+        <v>953.67</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1057.86</v>
+        <v>1060.76</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1911.67</v>
+        <v>1916.92</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>7120.21</v>
+        <v>7184.97</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4675.34</v>
+        <v>4717.87</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2061.11</v>
+        <v>2079.86</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>5381.24</v>
+        <v>5430.19</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>11586.65</v>
+        <v>11692.03</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>99802.16</v>
+        <v>100709.93</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>5396.05</v>
+        <v>5445.13</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>36109.28</v>
+        <v>36360.67</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1006.01</v>
+        <v>1013.01</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1460.29</v>
+        <v>1470.46</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>12309.3</v>
+        <v>12390.36</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>15243.16</v>
+        <v>15343.55</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2643.17</v>
+        <v>2638.64</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2653.25</v>
+        <v>2648.7</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>14260.69</v>
+        <v>14236.25</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>29166.96</v>
+        <v>29116.97</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1133.73</v>
+        <v>1125.61</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1271.66</v>
+        <v>1262.55</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1544.79</v>
+        <v>1533.72</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2491.82</v>
+        <v>2473.97</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2450.06</v>
+        <v>2432.51</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1089.44</v>
+        <v>1081.64</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3939.09</v>
+        <v>3910.87</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>2452.18</v>
+        <v>2434.61</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>23738.67</v>
+        <v>23703.75</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3688.2</v>
+        <v>3682.77</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>823.6</v>
+        <v>819.11</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>7713.28</v>
+        <v>7671.27</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1401.7</v>
+        <v>1394.07</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>31934.96</v>
+        <v>31746.77</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2590.45</v>
+        <v>2575.18</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>1402.24</v>
+        <v>1393.98</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>1047.69</v>
+        <v>1041.32</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1784.75</v>
+        <v>1773.9</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1099.02</v>
+        <v>1092.34</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>939.16</v>
+        <v>933.45</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1141.74</v>
+        <v>1134.8</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>7395.81</v>
+        <v>7350.87</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>4044.87</v>
+        <v>4020.3</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>1427.97</v>
+        <v>1419.29</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>3675.06</v>
+        <v>3652.73</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>8216.559999999999</v>
+        <v>8166.63</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>8343.690000000001</v>
+        <v>8292.99</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2359.53</v>
+        <v>2361.8</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>18473.18</v>
+        <v>18490.98</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1193.94</v>
+        <v>1195.09</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>14129.6</v>
+        <v>14143.22</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>13376.72</v>
+        <v>13389.61</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2515.02</v>
+        <v>2517.45</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4774.83</v>
+        <v>4779.43</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2185.1</v>
+        <v>2187.21</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>3613.79</v>
+        <v>3617.27</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>5671.56</v>
+        <v>5677.03</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>4695.83</v>
+        <v>4700.36</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>2655.39</v>
+        <v>2657.95</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>7640.77</v>
+        <v>7648.14</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>2417.87</v>
+        <v>2427.4</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3158.74</v>
+        <v>3171.19</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>53921.66</v>
+        <v>54134.25</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>975.0599999999999</v>
+        <v>978.9</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>2678.96</v>
+        <v>2689.52</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>5133.68</v>
+        <v>5153.92</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>6911.6</v>
+        <v>6938.85</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2876.72</v>
+        <v>2888.06</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>3686.2</v>
+        <v>3700.73</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>6644.74</v>
+        <v>6670.93</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>22096.02</v>
+        <v>22460.2</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>17672.38</v>
+        <v>17963.65</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>6174.35</v>
+        <v>6276.11</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>32703.06</v>
+        <v>33242.06</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>31234.11</v>
+        <v>31748.89</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1968.92</v>
+        <v>1973.77</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5346.78</v>
+        <v>5359.94</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3230.04</v>
+        <v>3237.98</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2298.43</v>
+        <v>2304.09</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>18826.54</v>
+        <v>18584.17</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>9394.15</v>
+        <v>9273.200000000001</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2285.54</v>
+        <v>2256.12</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>11342.21</v>
+        <v>11196.19</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>12781.65</v>
+        <v>12617.1</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>10311.63</v>
+        <v>10178.87</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>7197.77</v>
+        <v>7105.1</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>29371.59</v>
+        <v>28993.46</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>14472.21</v>
+        <v>14370.08</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>13242.63</v>
+        <v>13149.17</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1119.25</v>
+        <v>1139.55</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>11924.48</v>
+        <v>12140.68</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1985.31</v>
+        <v>2021.3</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1559.86</v>
+        <v>1588.14</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>3051.46</v>
+        <v>3106.78</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>16701.96</v>
+        <v>16963.59</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1687.73</v>
+        <v>1714.16</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>780.2</v>
+        <v>780.16</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1862.66</v>
+        <v>1864.26</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1173.76</v>
+        <v>1178.61</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2166.85</v>
+        <v>2175.8</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2772.03</v>
+        <v>2783.48</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>36014.88</v>
+        <v>36163.66</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1797.76</v>
+        <v>1805.18</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>6621.39</v>
+        <v>6648.75</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>45375.76</v>
+        <v>45563.21</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3125.32</v>
+        <v>3138.23</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1337.67</v>
+        <v>1333.98</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1378.55</v>
+        <v>1374.75</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>75974.75</v>
+        <v>75097.67</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>5605.05</v>
+        <v>5540.35</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2286.51</v>
+        <v>2252.41</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3439.26</v>
+        <v>3417.23</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2085.92</v>
+        <v>2072.55</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>8252.67</v>
+        <v>8199.790000000001</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>780.04</v>
+        <v>775.04</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2666.45</v>
+        <v>2649.37</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>959.5700000000001</v>
+        <v>953.42</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1069.26</v>
+        <v>1062.41</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>837.2</v>
+        <v>831.83</v>
       </c>
     </row>
     <row r="323">
@@ -20150,13 +20150,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>3099.93</v>
+        <v>3080.07</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>3390-97-CM26</t>
+          <t>3390-101-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20196,12 +20196,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
+          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.965.620-9</t>
+          <t>79.984.240-8</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>3093.77</v>
+        <v>779.59</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2141.46</v>
+        <v>2127.74</v>
       </c>
     </row>
     <row r="326">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2884.95</v>
+        <v>2866.47</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3390-101-CM26</t>
+          <t>3390-97-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>AGROSUPER COMERCIALIZADORA DE ALIMENTOS LTDA</t>
+          <t>IMPORTADORA Y ALIMENTOS ICB FOOD SERVICE SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>79.984.240-8</t>
+          <t>77.965.620-9</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>784.62</v>
+        <v>3073.95</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>6954.8</v>
+        <v>6910.24</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2698.12</v>
+        <v>2680.83</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>1695.01</v>
+        <v>1684.15</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1339.72</v>
+        <v>1331.13</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>2830</v>
+        <v>2811.87</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>11774.82</v>
+        <v>11699.38</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>4574.62</v>
+        <v>4554.91</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>8467.389999999999</v>
+        <v>8430.92</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>1307.85</v>
+        <v>1302.21</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1496.88</v>
+        <v>1475.22</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>2989.61</v>
+        <v>2946.36</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>4359.85</v>
+        <v>4296.78</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2007.6</v>
+        <v>1978.55</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>14383.09</v>
+        <v>14175.01</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>7046.28</v>
+        <v>6944.34</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1097.71</v>
+        <v>1081.83</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>33274.03</v>
+        <v>32792.65</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>1270.48</v>
+        <v>1252.1</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>4833.53</v>
+        <v>4763.61</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>52267.71</v>
+        <v>51511.55</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>16217.73</v>
+        <v>15983.11</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>1291.18</v>
+        <v>1272.5</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4272.95</v>
+        <v>4211.13</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>3994.17</v>
+        <v>3936.39</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>4574.82</v>
+        <v>4476.4</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>2602.09</v>
+        <v>2546.1</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>3047.43</v>
+        <v>2981.87</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>68074.35000000001</v>
+        <v>66609.73</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>48908.1</v>
+        <v>47348.57</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6631.76</v>
+        <v>6420.29</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>6390.02</v>
+        <v>6186.26</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>4293.42</v>
+        <v>4156.51</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1051.04</v>
+        <v>1030.31</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>6096.04</v>
+        <v>5975.82</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>15221.53</v>
+        <v>14921.34</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2564.5</v>
+        <v>2513.92</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>1549.75</v>
+        <v>1519.19</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1375.46</v>
+        <v>1339.24</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1709.1</v>
+        <v>1664.09</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1106.49</v>
+        <v>1077.35</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>1025.21</v>
+        <v>1006.62</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1938.14</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>779.45</v>
+        <v>765.3099999999999</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1218.95</v>
+        <v>1196.85</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>1425.48</v>
+        <v>1399.63</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>1074.5</v>
+        <v>1055.01</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>4260.93</v>
+        <v>4183.66</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>10774.24</v>
+        <v>10578.85</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>11779.38</v>
+        <v>11565.76</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>3144.57</v>
+        <v>3087.54</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1271.29</v>
+        <v>1248.23</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1217.17</v>
+        <v>1195.1</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>34194</v>
+        <v>33278.41</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>4042.98</v>
+        <v>3934.72</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>1732.6</v>
+        <v>1686.21</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>4938.35</v>
+        <v>4806.12</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>21390.8</v>
+        <v>21479.7</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2461.34</v>
+        <v>2471.57</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>783.5700000000001</v>
+        <v>786.83</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>3703.64</v>
+        <v>3719.04</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>5880.47</v>
+        <v>5930.38</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>4222.81</v>
+        <v>4258.65</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3376</v>
+        <v>3404.65</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>35809.94</v>
+        <v>36113.86</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>2751.43</v>
+        <v>2746.83</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>1596.1</v>
+        <v>1615.74</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>13419.24</v>
+        <v>13584.39</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>14665.74</v>
+        <v>14846.24</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>5940.62</v>
+        <v>6013.73</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>1188.79</v>
+        <v>1204.62</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2717.25</v>
+        <v>2753.42</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>15238.43</v>
+        <v>15613.45</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>3630.75</v>
+        <v>3720.1</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>2105.8</v>
+        <v>2129.75</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2865.1</v>
+        <v>2897.68</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>20957.22</v>
+        <v>21195.55</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>13276.63</v>
+        <v>13427.61</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>67870.09</v>
+        <v>68151.39999999999</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>54502.23</v>
+        <v>54728.13</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>37450.46</v>
+        <v>37605.68</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3114.96</v>
+        <v>3127.87</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>6076.38</v>
+        <v>6101.57</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>3395.48</v>
+        <v>3409.56</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2490.32</v>
+        <v>2500.64</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>850.89</v>
+        <v>854.41</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1458.98</v>
+        <v>1465.03</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2866.73</v>
+        <v>2878.62</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>2647.94</v>
+        <v>2658.92</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>2004.37</v>
+        <v>2012.68</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>894.0700000000001</v>
+        <v>897.78</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>2038.84</v>
+        <v>2043.07</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4103.53</v>
+        <v>4112.03</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>30824.12</v>
+        <v>30887.97</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>1054.92</v>
+        <v>1057.1</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>990.77</v>
+        <v>992.8200000000001</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>23161.6</v>
+        <v>23209.58</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>8908.48</v>
+        <v>8926.93</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>3361.56</v>
+        <v>3368.53</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>13851.79</v>
+        <v>13880.48</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3805.6</v>
+        <v>3813.49</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>34567.01</v>
+        <v>34418.51</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>860.3200000000001</v>
+        <v>856.62</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>891.45</v>
+        <v>887.62</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>1534.58</v>
+        <v>1527.99</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>10803.12</v>
+        <v>10756.72</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>3430.37</v>
+        <v>3415.64</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>4731.11</v>
+        <v>4710.79</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>8691.75</v>
+        <v>8654.41</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>1479.88</v>
+        <v>1473.52</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>1606.08</v>
+        <v>1599.18</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>10689.77</v>
+        <v>10643.85</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>4593.66</v>
+        <v>4573.93</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>1835.82</v>
+        <v>1810.86</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>8518.139999999999</v>
+        <v>8402.33</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>22270.26</v>
+        <v>21967.48</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5235.43</v>
+        <v>5164.25</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>10805.18</v>
+        <v>10713.02</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>2983.08</v>
+        <v>2957.64</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1361.77</v>
+        <v>1350.15</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2378.9</v>
+        <v>2358.61</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1728.69</v>
+        <v>1713.94</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>4282.35</v>
+        <v>4245.82</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2021.69</v>
+        <v>2004.45</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>2279.23</v>
+        <v>2259.79</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2620.18</v>
+        <v>2649.48</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>3141.75</v>
+        <v>3176.89</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1028.89</v>
+        <v>1040.4</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2008.97</v>
+        <v>2031.44</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1413.3</v>
+        <v>1429.11</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>1389.18</v>
+        <v>1394.44</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2293.62</v>
+        <v>2302.31</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>3072.27</v>
+        <v>3083.91</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>21266.14</v>
+        <v>21346.71</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>2235.52</v>
+        <v>2243.99</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>1992.84</v>
+        <v>2000.39</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>2150.78</v>
+        <v>2158.93</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>1617.04</v>
+        <v>1623.17</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>953.83</v>
+        <v>957.45</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>1445.44</v>
+        <v>1450.91</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>8515.790000000001</v>
+        <v>8494.290000000001</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>3113.92</v>
+        <v>3106.05</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>863.54</v>
+        <v>861.36</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1564.65</v>
+        <v>1560.7</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>10962.77</v>
+        <v>11066.93</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>11400.97</v>
+        <v>11509.28</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>863.73</v>
+        <v>871.9400000000001</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>16926.94</v>
+        <v>17087.75</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>15160.26</v>
+        <v>15273.2</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>6116.97</v>
+        <v>6162.54</v>
       </c>
     </row>
     <row r="477">
@@ -29544,13 +29544,13 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>2941.31</v>
+        <v>2911.97</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>4232-54-CM26</t>
+          <t>3483-188-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -29575,12 +29575,12 @@
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -29590,12 +29590,12 @@
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>COMERCIAL ESTEFITA LTDA.</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>76.030.335-6</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K478" t="inlineStr"/>
@@ -29605,13 +29605,13 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>5880.99</v>
+        <v>1002.34</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>4232-53-CM26</t>
+          <t>4232-54-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -29651,12 +29651,12 @@
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>Distribución y Logística S.A.</t>
+          <t>COMERCIAL ESTEFITA LTDA.</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>99.529.250-5</t>
+          <t>76.030.335-6</t>
         </is>
       </c>
       <c r="K479" t="inlineStr"/>
@@ -29666,13 +29666,13 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>6794.32</v>
+        <v>5855.21</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>3483-194-CM26</t>
+          <t>4232-53-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -29697,12 +29697,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -29712,12 +29712,12 @@
       </c>
       <c r="I480" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>Distribución y Logística S.A.</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>99.529.250-5</t>
         </is>
       </c>
       <c r="K480" t="inlineStr"/>
@@ -29727,13 +29727,13 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>5411.42</v>
+        <v>6764.54</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>4232-51-CM26</t>
+          <t>3483-194-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -29758,12 +29758,12 @@
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -29773,12 +29773,12 @@
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>15.009.829-7</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K481" t="inlineStr"/>
@@ -29788,13 +29788,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>7630.09</v>
+        <v>5387.7</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>3483-188-CM26</t>
+          <t>4232-51-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -29819,12 +29819,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29834,12 +29834,12 @@
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>15.009.829-7</t>
         </is>
       </c>
       <c r="K482" t="inlineStr"/>
@@ -29849,13 +29849,13 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>1006.75</v>
+        <v>7596.65</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>3483-187-CM26</t>
+          <t>3483-186-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -29875,7 +29875,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -29895,12 +29895,12 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>COMERCIALIZADORA ALSAN LIMITADA</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.420.496-4</t>
         </is>
       </c>
       <c r="K483" t="inlineStr"/>
@@ -29910,13 +29910,13 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>28375.86</v>
+        <v>925.48</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>3483-184-CM26</t>
+          <t>3483-187-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -29956,12 +29956,12 @@
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>UNIVERSAL FOOD SPA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>77.909.186-4</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K484" t="inlineStr"/>
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>6330.91</v>
+        <v>28251.48</v>
       </c>
     </row>
     <row r="485">
@@ -30032,13 +30032,13 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>1059.39</v>
+        <v>1054.75</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>3483-183-CM26</t>
+          <t>3483-184-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -30078,12 +30078,12 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>UNIVERSAL FOOD SPA</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>77.909.186-4</t>
         </is>
       </c>
       <c r="K486" t="inlineStr"/>
@@ -30093,13 +30093,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>3680.66</v>
+        <v>6303.16</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>3483-182-CM26</t>
+          <t>3483-183-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -30139,12 +30139,12 @@
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>CASO Y CIA SAC</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>92.423.000-2</t>
+          <t>77.008.207-2</t>
         </is>
       </c>
       <c r="K487" t="inlineStr"/>
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>16476.58</v>
+        <v>3664.53</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>3483-180-CM26</t>
+          <t>3483-182-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -30200,12 +30200,12 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>RUSTICO, MINIMARKET Y AMASANDERÍA SPA</t>
+          <t>CASO Y CIA SAC</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>77.344.062-K</t>
+          <t>92.423.000-2</t>
         </is>
       </c>
       <c r="K488" t="inlineStr"/>
@@ -30215,13 +30215,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>1448.25</v>
+        <v>16404.35</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>3483-179-CM26</t>
+          <t>3483-180-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -30261,12 +30261,12 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
+          <t>RUSTICO, MINIMARKET Y AMASANDERÍA SPA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>15.009.829-7</t>
+          <t>77.344.062-K</t>
         </is>
       </c>
       <c r="K489" t="inlineStr"/>
@@ -30276,13 +30276,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>1191.18</v>
+        <v>1441.9</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>3483-186-CM26</t>
+          <t>3483-179-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -30302,7 +30302,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -30322,12 +30322,12 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ALSAN LIMITADA</t>
+          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>76.420.496-4</t>
+          <t>15.009.829-7</t>
         </is>
       </c>
       <c r="K490" t="inlineStr"/>
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>929.55</v>
+        <v>1185.96</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>3308.96</v>
+        <v>3272.97</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>13920.72</v>
+        <v>13769.29</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1988.45</v>
+        <v>1983.54</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>6372.28</v>
+        <v>6356.54</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>2059.08</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>1215.63</v>
+        <v>1212.63</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>7827.21</v>
+        <v>7807.88</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>10116.66</v>
+        <v>10150.22</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2250.55</v>
+        <v>2258.01</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1798.82</v>
+        <v>1804.78</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>2439.74</v>
+        <v>2447.5</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>27368.28</v>
+        <v>27455.39</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>1245.91</v>
+        <v>1252.53</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1601.96</v>
+        <v>1610.48</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>926.91</v>
+        <v>931.84</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>838.17</v>
+        <v>842.62</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>795.63</v>
+        <v>799.86</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>11453.66</v>
+        <v>11514.56</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>4383.61</v>
+        <v>4406.91</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2654.99</v>
+        <v>2669.11</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1345.09</v>
+        <v>1352.24</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>964.75</v>
+        <v>969.88</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2369.39</v>
+        <v>2381.98</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>4234.71</v>
+        <v>4257.23</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1984.19</v>
+        <v>2012.58</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>985.63</v>
+        <v>999.73</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>797.45</v>
+        <v>806.8</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2612.08</v>
+        <v>2642.72</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2665.53</v>
+        <v>2696.8</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1743.44</v>
+        <v>1763.9</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>22247.88</v>
+        <v>22624.15</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>12885.53</v>
+        <v>13103.46</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>17932.85</v>
+        <v>18236.14</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1218.09</v>
+        <v>1238.69</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>43709.96</v>
+        <v>44449.2</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>1816.28</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>6060.54</v>
+        <v>6163.04</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>809.16</v>
+        <v>822.84</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1302.44</v>
+        <v>1324.46</v>
       </c>
     </row>
     <row r="530">
@@ -32777,13 +32777,13 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>5004.75</v>
+        <v>5089.39</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>3340-129-CM26</t>
+          <t>3340-132-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -32823,12 +32823,12 @@
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>MARTA IRIS JORQUERA AGUILERA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>10.049.558-9</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K531" t="inlineStr"/>
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1845.87</v>
+        <v>56618.38</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>2259.97</v>
+        <v>2298.19</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>20699.94</v>
+        <v>21050.02</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>2761.93</v>
+        <v>2808.64</v>
       </c>
     </row>
     <row r="535">
@@ -33082,13 +33082,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>5405.54</v>
+        <v>5496.96</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>3340-132-CM26</t>
+          <t>3340-138-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>55676.75</v>
+        <v>14241.86</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>1115.17</v>
+        <v>1134.03</v>
       </c>
     </row>
     <row r="538">
@@ -33265,13 +33265,13 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>1457.36</v>
+        <v>1482.01</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>3340-128-CM26</t>
+          <t>3340-129-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -33311,12 +33311,12 @@
       </c>
       <c r="I539" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>MARTA IRIS JORQUERA AGUILERA</t>
         </is>
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>10.049.558-9</t>
         </is>
       </c>
       <c r="K539" t="inlineStr"/>
@@ -33326,13 +33326,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>8402.48</v>
+        <v>1877.09</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>3340-138-CM26</t>
+          <t>3340-128-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -33387,13 +33387,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>14005</v>
+        <v>8544.58</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>5702-400-CM26</t>
+          <t>5702-399-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -33433,12 +33433,12 @@
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>BYRON ARANCIBIA E.I.R.L.</t>
+          <t>BIDFOOD CHILE S.A.</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>77.146.606-0</t>
+          <t>76.111.152-3</t>
         </is>
       </c>
       <c r="K541" t="inlineStr"/>
@@ -33448,13 +33448,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>2009.11</v>
+        <v>2086.8</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>5702-399-CM26</t>
+          <t>5702-398-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
@@ -33494,12 +33494,12 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>BIDFOOD CHILE S.A.</t>
+          <t>Sociedad Comercial Arauco Ltda.</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>76.111.152-3</t>
+          <t>78.108.500-6</t>
         </is>
       </c>
       <c r="K542" t="inlineStr"/>
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2065.79</v>
+        <v>62412.64</v>
       </c>
     </row>
     <row r="543">
@@ -33570,13 +33570,13 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>1024.25</v>
+        <v>1034.66</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>5702-398-CM26</t>
+          <t>5702-400-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -33596,7 +33596,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
@@ -33616,12 +33616,12 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Arauco Ltda.</t>
+          <t>BYRON ARANCIBIA E.I.R.L.</t>
         </is>
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>78.108.500-6</t>
+          <t>77.146.606-0</t>
         </is>
       </c>
       <c r="K544" t="inlineStr"/>
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>61784.34</v>
+        <v>2029.54</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>10561.92</v>
+        <v>10669.33</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>33846.78</v>
+        <v>34190.98</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>51336.96</v>
+        <v>51859.02</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>1083.15</v>
+        <v>1094.16</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>12920.17</v>
+        <v>13041.35</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>1041.42</v>
+        <v>1051.18</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>3842</v>
+        <v>3878.03</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>2425.55</v>
+        <v>2407.14</v>
       </c>
     </row>
     <row r="553">
@@ -34180,13 +34180,13 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>2356.08</v>
+        <v>2338.2</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>5702-392-CM26</t>
+          <t>5702-414-CM26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -34226,12 +34226,12 @@
       </c>
       <c r="I554" t="inlineStr">
         <is>
-          <t>alimentos y frutos</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>96.557.910-9</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K554" t="inlineStr"/>
@@ -34241,13 +34241,13 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>4088.74</v>
+        <v>12368.41</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>3459-160-CM26</t>
+          <t>3483-221-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -34272,7 +34272,7 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -34287,12 +34287,12 @@
       </c>
       <c r="I555" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>RUSTICO, MINIMARKET Y AMASANDERÍA SPA</t>
         </is>
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>77.344.062-K</t>
         </is>
       </c>
       <c r="K555" t="inlineStr"/>
@@ -34302,13 +34302,13 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>1456.31</v>
+        <v>1969.64</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>3483-221-CM26</t>
+          <t>3459-160-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -34333,7 +34333,7 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -34348,12 +34348,12 @@
       </c>
       <c r="I556" t="inlineStr">
         <is>
-          <t>RUSTICO, MINIMARKET Y AMASANDERÍA SPA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>77.344.062-K</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K556" t="inlineStr"/>
@@ -34363,13 +34363,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2003.49</v>
+        <v>1431.71</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>5702-414-CM26</t>
+          <t>5702-392-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -34409,12 +34409,12 @@
       </c>
       <c r="I557" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>alimentos y frutos</t>
         </is>
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>96.557.910-9</t>
         </is>
       </c>
       <c r="K557" t="inlineStr"/>
@@ -34424,13 +34424,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>12580.97</v>
+        <v>4019.65</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>3340-136-CM26</t>
+          <t>3390-188-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>65.286.850-9</t>
+          <t>61.962.500-5</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -34470,12 +34470,12 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
+          <t>Sociedad Comercial Arauco Ltda.</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>15.009.829-7</t>
+          <t>78.108.500-6</t>
         </is>
       </c>
       <c r="K558" t="inlineStr"/>
@@ -34485,13 +34485,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>84623.34</v>
+        <v>1234.2</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>3390-188-CM26</t>
+          <t>3340-136-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -34516,7 +34516,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>61.962.500-5</t>
+          <t>65.286.850-9</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -34531,12 +34531,12 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Arauco Ltda.</t>
+          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>78.108.500-6</t>
+          <t>15.009.829-7</t>
         </is>
       </c>
       <c r="K559" t="inlineStr"/>
@@ -34546,7 +34546,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1251.39</v>
+        <v>83460.59</v>
       </c>
     </row>
     <row r="560">
@@ -34607,13 +34607,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2196.83</v>
+        <v>2166.65</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>3483-212-CM26</t>
+          <t>3483-197-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -34653,12 +34653,12 @@
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>Sociedad Comercial Arauco Ltda.</t>
         </is>
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>78.108.500-6</t>
         </is>
       </c>
       <c r="K561" t="inlineStr"/>
@@ -34668,13 +34668,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1207.9</v>
+        <v>15103.41</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>3483-197-CM26</t>
+          <t>3483-212-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -34714,12 +34714,12 @@
       </c>
       <c r="I562" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Arauco Ltda.</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>78.108.500-6</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K562" t="inlineStr"/>
@@ -34729,13 +34729,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>15035.13</v>
+        <v>1213.39</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>5702-426-CM26</t>
+          <t>1272219-29-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -34760,12 +34760,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -34775,12 +34775,12 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>Distribución y Logística S.A.</t>
+          <t>CASO Y CIA SAC</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>99.529.250-5</t>
+          <t>92.423.000-2</t>
         </is>
       </c>
       <c r="K563" t="inlineStr"/>
@@ -34790,13 +34790,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>1883.84</v>
+        <v>1240.27</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>1272219-27-CM26</t>
+          <t>5702-432-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -34816,17 +34816,17 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -34836,12 +34836,12 @@
       </c>
       <c r="I564" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>Sociedad Comercial Arauco Ltda.</t>
         </is>
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>78.108.500-6</t>
         </is>
       </c>
       <c r="K564" t="inlineStr"/>
@@ -34851,7 +34851,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>24710.03</v>
+        <v>5789.9</v>
       </c>
     </row>
     <row r="565">
@@ -34912,13 +34912,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>1705.81</v>
+        <v>1731.21</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>1272219-29-CM26</t>
+          <t>1272219-27-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -34938,7 +34938,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -34958,12 +34958,12 @@
       </c>
       <c r="I566" t="inlineStr">
         <is>
-          <t>CASO Y CIA SAC</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>92.423.000-2</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K566" t="inlineStr"/>
@@ -34973,13 +34973,13 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>1222.07</v>
+        <v>25077.97</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>5702-432-CM26</t>
+          <t>5702-426-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -35019,12 +35019,12 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Arauco Ltda.</t>
+          <t>Distribución y Logística S.A.</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>78.108.500-6</t>
+          <t>99.529.250-5</t>
         </is>
       </c>
       <c r="K567" t="inlineStr"/>
@@ -35034,7 +35034,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>5704.95</v>
+        <v>1911.89</v>
       </c>
     </row>
     <row r="568">
@@ -35095,7 +35095,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>4831.67</v>
+        <v>4923.53</v>
       </c>
     </row>
     <row r="569">
@@ -35156,7 +35156,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>11725.9</v>
+        <v>11990.35</v>
       </c>
     </row>
     <row r="570">
@@ -35217,7 +35217,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>13832.18</v>
+        <v>14144.13</v>
       </c>
     </row>
     <row r="571">
@@ -35278,13 +35278,13 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>2126.79</v>
+        <v>2174.76</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>1075963-8036-CM26</t>
+          <t>1075963-8032-CM26</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -35304,7 +35304,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -35324,12 +35324,12 @@
       </c>
       <c r="I572" t="inlineStr">
         <is>
-          <t>COMERCIAL ESTEFITA LTDA.</t>
+          <t>Distribución y Logística S.A.</t>
         </is>
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>76.030.335-6</t>
+          <t>99.529.250-5</t>
         </is>
       </c>
       <c r="K572" t="inlineStr"/>
@@ -35339,13 +35339,13 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>2552.24</v>
+        <v>1355.9</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>1075963-8032-CM26</t>
+          <t>1075963-8036-CM26</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -35365,7 +35365,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -35385,12 +35385,12 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>Distribución y Logística S.A.</t>
+          <t>COMERCIAL ESTEFITA LTDA.</t>
         </is>
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>99.529.250-5</t>
+          <t>76.030.335-6</t>
         </is>
       </c>
       <c r="K573" t="inlineStr"/>
@@ -35400,7 +35400,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>1346.6</v>
+        <v>2569.86</v>
       </c>
     </row>
     <row r="574">
@@ -35461,7 +35461,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>860.1</v>
+        <v>862.76</v>
       </c>
     </row>
     <row r="575">
@@ -35522,7 +35522,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>1999.04</v>
+        <v>2005.22</v>
       </c>
     </row>
     <row r="576">
@@ -35583,7 +35583,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>863.42</v>
+        <v>861.14</v>
       </c>
     </row>
     <row r="577">
@@ -35644,7 +35644,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>3324.1</v>
+        <v>3315.31</v>
       </c>
     </row>
     <row r="578">
@@ -35705,7 +35705,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>1959.78</v>
+        <v>1954.59</v>
       </c>
     </row>
     <row r="579">
@@ -35766,7 +35766,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>863.42</v>
+        <v>861.14</v>
       </c>
     </row>
     <row r="580">
@@ -35827,7 +35827,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>1064.26</v>
+        <v>1061.45</v>
       </c>
     </row>
     <row r="581">
@@ -35888,13 +35888,13 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>11069.25</v>
+        <v>10905.25</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>3459-174-CM26</t>
+          <t>1075963-8025-CM26</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -35919,12 +35919,12 @@
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>65.287.570-K</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
@@ -35934,12 +35934,12 @@
       </c>
       <c r="I582" t="inlineStr">
         <is>
-          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
+          <t>Distribución y Logística S.A.</t>
         </is>
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>76.371.396-2</t>
+          <t>99.529.250-5</t>
         </is>
       </c>
       <c r="K582" t="inlineStr"/>
@@ -35949,13 +35949,13 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>20207.35</v>
+        <v>1943.41</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>3459-171-CM26</t>
+          <t>3459-174-CM26</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -35995,12 +35995,12 @@
       </c>
       <c r="I583" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
         </is>
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.371.396-2</t>
         </is>
       </c>
       <c r="K583" t="inlineStr"/>
@@ -36010,13 +36010,13 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>20611.6</v>
+        <v>19792.05</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>1075963-8025-CM26</t>
+          <t>3459-171-CM26</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -36041,12 +36041,12 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>65.287.570-K</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -36056,12 +36056,12 @@
       </c>
       <c r="I584" t="inlineStr">
         <is>
-          <t>Distribución y Logística S.A.</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>99.529.250-5</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K584" t="inlineStr"/>
@@ -36071,7 +36071,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>1984.19</v>
+        <v>20188</v>
       </c>
     </row>
     <row r="585">
@@ -36132,7 +36132,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>21346.35</v>
+        <v>21549.12</v>
       </c>
     </row>
     <row r="586">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1422.17</v>
+        <v>1435.68</v>
       </c>
     </row>
     <row r="587">
@@ -36254,7 +36254,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1148.05</v>
+        <v>1158.96</v>
       </c>
     </row>
     <row r="588">
@@ -36315,7 +36315,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>3235.29</v>
+        <v>3266.02</v>
       </c>
     </row>
     <row r="589">
@@ -36376,7 +36376,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>15285.78</v>
+        <v>15430.98</v>
       </c>
     </row>
     <row r="590">
@@ -36437,13 +36437,13 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>2106.19</v>
+        <v>2126.2</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>5702-475-CM26</t>
+          <t>5702-469-CM26</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -36463,7 +36463,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
@@ -36483,12 +36483,12 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
+          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
         </is>
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>15.009.829-7</t>
+          <t>76.371.396-2</t>
         </is>
       </c>
       <c r="K591" t="inlineStr"/>
@@ -36498,7 +36498,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>802.38</v>
+        <v>861.29</v>
       </c>
     </row>
     <row r="592">
@@ -36559,7 +36559,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>23906.25</v>
+        <v>23999.57</v>
       </c>
     </row>
     <row r="593">
@@ -36620,13 +36620,13 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>4865.86</v>
+        <v>4884.86</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>5702-469-CM26</t>
+          <t>5702-470-CM26</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -36646,7 +36646,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
+          <t>BYRON ARANCIBIA E.I.R.L.</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>76.371.396-2</t>
+          <t>77.146.606-0</t>
         </is>
       </c>
       <c r="K594" t="inlineStr"/>
@@ -36681,13 +36681,13 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>857.9400000000001</v>
+        <v>1302.27</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>5702-470-CM26</t>
+          <t>5702-472-CM26</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -36727,12 +36727,12 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>BYRON ARANCIBIA E.I.R.L.</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>77.146.606-0</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K595" t="inlineStr"/>
@@ -36742,13 +36742,13 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>1297.21</v>
+        <v>7525.47</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>5702-472-CM26</t>
+          <t>5702-473-CM26</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -36788,12 +36788,12 @@
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K596" t="inlineStr"/>
@@ -36803,13 +36803,13 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>7496.2</v>
+        <v>772.79</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>5702-473-CM26</t>
+          <t>5702-474-CM26</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -36849,12 +36849,12 @@
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>MARTA IRIS JORQUERA AGUILERA</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>10.049.558-9</t>
         </is>
       </c>
       <c r="K597" t="inlineStr"/>
@@ -36864,13 +36864,13 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>769.79</v>
+        <v>1381.11</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>5702-474-CM26</t>
+          <t>5702-475-CM26</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -36910,12 +36910,12 @@
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>MARTA IRIS JORQUERA AGUILERA</t>
+          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>10.049.558-9</t>
+          <t>15.009.829-7</t>
         </is>
       </c>
       <c r="K598" t="inlineStr"/>
@@ -36925,7 +36925,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1375.74</v>
+        <v>805.51</v>
       </c>
     </row>
     <row r="599">
@@ -36986,13 +36986,13 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>11884.38</v>
+        <v>12003.91</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>5702-480-CM26</t>
+          <t>5702-484-CM26</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -37012,7 +37012,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
@@ -37032,12 +37032,12 @@
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t xml:space="preserve">IZZAMAR AHOLIBAMA BASEMAT </t>
+          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>76.628.675-5</t>
+          <t>76.371.396-2</t>
         </is>
       </c>
       <c r="K600" t="inlineStr"/>
@@ -37047,13 +37047,13 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>6278.4</v>
+        <v>964.84</v>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>5702-485-CM26</t>
+          <t>3185-87-CM26</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -37078,12 +37078,12 @@
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.102.001-5</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>GOBERNACION MARITIMA DE ARICA</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -37093,12 +37093,12 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>BYRON ARANCIBIA E.I.R.L.</t>
+          <t>PROVER LTDA</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>77.146.606-0</t>
+          <t>76.231.675-7</t>
         </is>
       </c>
       <c r="K601" t="inlineStr"/>
@@ -37108,13 +37108,13 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>1949.58</v>
+        <v>3378.86</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>3185-87-CM26</t>
+          <t>5702-482-CM26</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -37134,17 +37134,17 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>61.102.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
@@ -37154,12 +37154,12 @@
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>PROVER LTDA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>76.231.675-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K602" t="inlineStr"/>
@@ -37169,13 +37169,13 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3345.22</v>
+        <v>9118.34</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>5702-484-CM26</t>
+          <t>5702-485-CM26</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -37195,7 +37195,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -37215,12 +37215,12 @@
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
+          <t>BYRON ARANCIBIA E.I.R.L.</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>76.371.396-2</t>
+          <t>77.146.606-0</t>
         </is>
       </c>
       <c r="K603" t="inlineStr"/>
@@ -37230,13 +37230,13 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>955.23</v>
+        <v>1969.19</v>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>5702-478-CM26</t>
+          <t>5702-480-CM26</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -37256,7 +37256,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
@@ -37276,12 +37276,12 @@
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t xml:space="preserve">IZZAMAR AHOLIBAMA BASEMAT </t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>76.628.675-5</t>
         </is>
       </c>
       <c r="K604" t="inlineStr"/>
@@ -37291,7 +37291,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>69583.57000000001</v>
+        <v>6341.54</v>
       </c>
     </row>
     <row r="605">
@@ -37352,7 +37352,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>5091.35</v>
+        <v>5142.55</v>
       </c>
     </row>
     <row r="606">
@@ -37413,13 +37413,13 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>21338.21</v>
+        <v>21552.82</v>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>5702-482-CM26</t>
+          <t>5702-478-CM26</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -37459,12 +37459,12 @@
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K607" t="inlineStr"/>
@@ -37474,7 +37474,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>9027.540000000001</v>
+        <v>70283.41</v>
       </c>
     </row>
     <row r="608">
@@ -37535,7 +37535,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>10585.73</v>
+        <v>10691.74</v>
       </c>
     </row>
     <row r="609">
@@ -37596,13 +37596,13 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>56652.38</v>
+        <v>57219.68</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>3483-230-CM26</t>
+          <t>5420-98-CM26</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -37627,12 +37627,12 @@
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>65.286.830-4</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
@@ -37642,12 +37642,12 @@
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>BIBAJ SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>77.312.033-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K610" t="inlineStr"/>
@@ -37657,13 +37657,13 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>1636.97</v>
+        <v>774.46</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>5702-492-CM26</t>
+          <t>5420-97-CM26</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -37688,12 +37688,12 @@
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -37703,12 +37703,12 @@
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>PROVER LTDA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>76.231.675-7</t>
+          <t>77.362.622-7</t>
         </is>
       </c>
       <c r="K611" t="inlineStr"/>
@@ -37718,13 +37718,13 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>2134.33</v>
+        <v>896.5599999999999</v>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>5420-97-CM26</t>
+          <t>3483-230-CM26</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -37749,12 +37749,12 @@
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>65.286.830-4</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -37764,12 +37764,12 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>BIBAJ SPA</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
+          <t>77.312.033-1</t>
         </is>
       </c>
       <c r="K612" t="inlineStr"/>
@@ -37779,13 +37779,13 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>892.01</v>
+        <v>1645.31</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>5420-98-CM26</t>
+          <t>5702-492-CM26</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -37810,12 +37810,12 @@
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -37825,12 +37825,12 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVER LTDA</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.231.675-7</t>
         </is>
       </c>
       <c r="K613" t="inlineStr"/>
@@ -37840,7 +37840,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>770.53</v>
+        <v>2145.21</v>
       </c>
     </row>
     <row r="614">
@@ -37901,7 +37901,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>991.35</v>
+        <v>997.8200000000001</v>
       </c>
     </row>
     <row r="615">
@@ -37962,7 +37962,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>11365</v>
+        <v>11391.06</v>
       </c>
     </row>
     <row r="616">
@@ -38023,7 +38023,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>13504.48</v>
+        <v>13598.99</v>
       </c>
     </row>
     <row r="617">
@@ -38084,7 +38084,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>4868.92</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="618">
@@ -38145,7 +38145,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>6191.5</v>
+        <v>6171.94</v>
       </c>
     </row>
     <row r="619">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>2397.26</v>
+        <v>2392.05</v>
       </c>
     </row>
     <row r="620">
@@ -38267,7 +38267,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>8780.629999999999</v>
+        <v>8638.93</v>
       </c>
     </row>
     <row r="621">
@@ -38328,13 +38328,13 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1222.92</v>
+        <v>1203.31</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>1346279-94-CM26</t>
+          <t>1346279-95-CM26</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -38354,7 +38354,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
@@ -38374,12 +38374,12 @@
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Arauco Ltda.</t>
+          <t>BIBAJ SPA</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>78.108.500-6</t>
+          <t>77.312.033-1</t>
         </is>
       </c>
       <c r="K622" t="inlineStr"/>
@@ -38389,13 +38389,13 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>878.15</v>
+        <v>3445.78</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>1346279-95-CM26</t>
+          <t>1346279-94-CM26</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -38415,7 +38415,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
@@ -38435,12 +38435,12 @@
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>BIBAJ SPA</t>
+          <t>Sociedad Comercial Arauco Ltda.</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>77.312.033-1</t>
+          <t>78.108.500-6</t>
         </is>
       </c>
       <c r="K623" t="inlineStr"/>
@@ -38450,13 +38450,13 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>3486.35</v>
+        <v>867.9299999999999</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>1346279-96-CM26</t>
+          <t>1346279-99-CM26</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -38496,12 +38496,12 @@
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>NEMESIO PAIRO QUISPE</t>
+          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>10.073.366-8</t>
+          <t>15.009.829-7</t>
         </is>
       </c>
       <c r="K624" t="inlineStr"/>
@@ -38511,13 +38511,13 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>2899.23</v>
+        <v>1333.26</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>1272219-31-CM26</t>
+          <t>1346279-96-CM26</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -38542,12 +38542,12 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -38557,12 +38557,12 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>NEMESIO PAIRO QUISPE</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>10.073.366-8</t>
         </is>
       </c>
       <c r="K625" t="inlineStr"/>
@@ -38572,13 +38572,13 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>30119.74</v>
+        <v>2883.16</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>1346279-97-CM26</t>
+          <t>1272219-31-CM26</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -38603,12 +38603,12 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -38618,12 +38618,12 @@
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>76.371.396-2</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K626" t="inlineStr"/>
@@ -38633,13 +38633,13 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>859.14</v>
+        <v>29952.76</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>1272219-33-CM26</t>
+          <t>1346279-97-CM26</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -38664,12 +38664,12 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H627" t="inlineStr">
@@ -38679,12 +38679,12 @@
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>MARTA IRIS JORQUERA AGUILERA</t>
+          <t>PROCESADORA DE ALIMENTOS JOSÉ MOREIRA SILVAN EMPRESA INDIVIDUAL DE RES</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
         <is>
-          <t>10.049.558-9</t>
+          <t>76.371.396-2</t>
         </is>
       </c>
       <c r="K627" t="inlineStr"/>
@@ -38694,13 +38694,13 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>4292.94</v>
+        <v>854.37</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>1272219-34-CM26</t>
+          <t>1272219-33-CM26</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -38740,12 +38740,12 @@
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>CASO Y CIA SAC</t>
+          <t>MARTA IRIS JORQUERA AGUILERA</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>92.423.000-2</t>
+          <t>10.049.558-9</t>
         </is>
       </c>
       <c r="K628" t="inlineStr"/>
@@ -38755,13 +38755,13 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>1508.1</v>
+        <v>4269.14</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>1272219-35-CM26</t>
+          <t>1272219-34-CM26</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -38801,12 +38801,12 @@
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
+          <t>CASO Y CIA SAC</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>81.094.100-6</t>
+          <t>92.423.000-2</t>
         </is>
       </c>
       <c r="K629" t="inlineStr"/>
@@ -38816,13 +38816,13 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>1557.52</v>
+        <v>1499.74</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>1346279-98-CM26</t>
+          <t>1272219-35-CM26</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -38847,12 +38847,12 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H630" t="inlineStr">
@@ -38877,13 +38877,13 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>1012.19</v>
+        <v>1548.88</v>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>1272219-38-CM26</t>
+          <t>1346279-98-CM26</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -38908,12 +38908,12 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>61.979.880-5</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Economato del Complejo Penitenciario de Arica</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
@@ -38923,12 +38923,12 @@
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COOP AGRICOLA Y LECHERA DE LA UNION LTDA</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>81.094.100-6</t>
         </is>
       </c>
       <c r="K631" t="inlineStr"/>
@@ -38938,13 +38938,13 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>1353.43</v>
+        <v>1006.57</v>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>1346279-99-CM26</t>
+          <t>1272219-38-CM26</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -38969,12 +38969,12 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.979.880-5</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Economato del Complejo Penitenciario de Arica</t>
         </is>
       </c>
       <c r="H632" t="inlineStr">
@@ -38984,12 +38984,12 @@
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>15.009.829-7</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K632" t="inlineStr"/>
@@ -38999,13 +38999,13 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>1340.7</v>
+        <v>1345.92</v>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>5702-536-CM26</t>
+          <t>5702-538-CM26</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -39045,12 +39045,12 @@
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>MARTA IRIS JORQUERA AGUILERA</t>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>10.049.558-9</t>
+          <t>16.770.707-6</t>
         </is>
       </c>
       <c r="K633" t="inlineStr"/>
@@ -39060,13 +39060,13 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>4027.04</v>
+        <v>64151.83</v>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>5702-538-CM26</t>
+          <t>5702-536-CM26</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -39106,12 +39106,12 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+          <t>MARTA IRIS JORQUERA AGUILERA</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>16.770.707-6</t>
+          <t>10.049.558-9</t>
         </is>
       </c>
       <c r="K634" t="inlineStr"/>
@@ -39121,13 +39121,13 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>64468.8</v>
+        <v>4007.24</v>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>5702-543-CM26</t>
+          <t>1075963-9308-CM26</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -39147,17 +39147,17 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>61.979.020-0</t>
+          <t>61.606.001-5</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39167,12 +39167,12 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>alimentos y frutos</t>
+          <t>Distribución y Logística S.A.</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>96.557.910-9</t>
+          <t>99.529.250-5</t>
         </is>
       </c>
       <c r="K635" t="inlineStr"/>
@@ -39182,13 +39182,13 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>4229.03</v>
+        <v>1837.56</v>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>5702-542-CM26</t>
+          <t>5702-541-CM26</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -39228,12 +39228,12 @@
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>Distribución y Logística S.A.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>99.529.250-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K636" t="inlineStr"/>
@@ -39243,13 +39243,13 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>2940.32</v>
+        <v>6389.63</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>5702-545-CM26</t>
+          <t>5702-542-CM26</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -39289,12 +39289,12 @@
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t xml:space="preserve">IZZAMAR AHOLIBAMA BASEMAT </t>
+          <t>Distribución y Logística S.A.</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>76.628.675-5</t>
+          <t>99.529.250-5</t>
         </is>
       </c>
       <c r="K637" t="inlineStr"/>
@@ -39304,13 +39304,13 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>2498.52</v>
+        <v>2960.01</v>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>1075963-9308-CM26</t>
+          <t>5702-543-CM26</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -39330,17 +39330,17 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>61.606.001-5</t>
+          <t>61.979.020-0</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARICA HOSP DR JUAN NOE CREVANI</t>
+          <t>Direc.Reg.Arica y Parinacota</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -39350,12 +39350,12 @@
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>Distribución y Logística S.A.</t>
+          <t>alimentos y frutos</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>99.529.250-5</t>
+          <t>96.557.910-9</t>
         </is>
       </c>
       <c r="K638" t="inlineStr"/>
@@ -39365,13 +39365,13 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1825.34</v>
+        <v>4257.34</v>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>5702-541-CM26</t>
+          <t>5702-545-CM26</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -39411,12 +39411,12 @@
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t xml:space="preserve">IZZAMAR AHOLIBAMA BASEMAT </t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.628.675-5</t>
         </is>
       </c>
       <c r="K639" t="inlineStr"/>
@@ -39426,7 +39426,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>6347.14</v>
+        <v>2515.25</v>
       </c>
     </row>
     <row r="640">
@@ -39487,7 +39487,373 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>10846.8</v>
+        <v>10919.41</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>1272219-41-CM26</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>61.979.880-5</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>NEMESIO PAIRO QUISPE</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>10.073.366-8</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M641" s="2" t="n">
+        <v>5991.07</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>3390-309-CM26</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>COMERCIAL ESTEFITA LTDA.</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>76.030.335-6</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M642" s="2" t="n">
+        <v>1899.74</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>3390-327-CM26</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>AYLIN JANET BRICEÑO CHÁVEZ</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>15.009.829-7</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M643" s="2" t="n">
+        <v>7594.65</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>3390-329-CM26</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M644" s="2" t="n">
+        <v>4434.83</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>3390-323-CM26</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>61.962.500-5</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>PROVER LTDA</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>76.231.675-7</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M645" s="2" t="n">
+        <v>1698.87</v>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>3185-121-CM26</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2239-9-LR24</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>61.102.001-5</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>PAMELA VERÓNICA NAVARRETE JORQUERA</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>16.770.707-6</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr"/>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M646" s="2" t="n">
+        <v>3227.75</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/alimentos/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/alimentos/arica-y-parinacota.xlsx
@@ -6103,7 +6103,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7530,7 +7534,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22595,7 +22603,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42819,7 +42831,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48880,7 +48896,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59901,7 +59921,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K953" t="inlineStr"/>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L953" t="inlineStr">
         <is>
           <t>USD</t>
@@ -66950,7 +66974,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1066" t="inlineStr"/>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1066" t="inlineStr">
         <is>
           <t>USD</t>
@@ -67775,7 +67803,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1079" t="inlineStr"/>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1079" t="inlineStr">
         <is>
           <t>USD</t>
@@ -72844,7 +72876,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1160" t="inlineStr"/>
+      <c r="K1160" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -76397,7 +76433,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1217" t="inlineStr"/>
+      <c r="K1217" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -91276,7 +91316,11 @@
           <t>79.984.240-8</t>
         </is>
       </c>
-      <c r="K1456" t="inlineStr"/>
+      <c r="K1456" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L1456" t="inlineStr">
         <is>
           <t>USD</t>
